--- a/artfynd/S 209-2025 artfynd.xlsx
+++ b/artfynd/S 209-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97571090</v>
+        <v>135175716</v>
       </c>
       <c r="B6" t="n">
-        <v>58238</v>
+        <v>107789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,39 +1154,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klintaberget/Skybygget, Ög</t>
+          <t>Kolvtorpsvägen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558471</v>
+        <v>544644</v>
       </c>
       <c r="R6" t="n">
-        <v>6510056</v>
+        <v>6517365</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,12 +1224,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,67 +1238,77 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Patricia Karlsteen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Patricia Karlsteen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109553273</v>
+        <v>97571090</v>
       </c>
       <c r="B7" t="n">
-        <v>58602</v>
+        <v>58238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Getnäs, Ög</t>
+          <t>Klintaberget/Skybygget, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558205</v>
+        <v>558471</v>
       </c>
       <c r="R7" t="n">
-        <v>6509459</v>
+        <v>6510056</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,22 +1332,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,15 +1352,123 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>109553273</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Getnäs, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>558205</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6509459</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Håkan Karlsson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Håkan Karlsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 209-2025 artfynd.xlsx
+++ b/artfynd/S 209-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129698903</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129698953</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115620650</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134976479</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1259,6 +1284,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135175716</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97571090</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1469,8 +1504,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109553273</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 209-2025 artfynd.xlsx
+++ b/artfynd/S 209-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1041,7 +1041,7 @@
         <v>134976479</v>
       </c>
       <c r="B5" t="n">
-        <v>107789</v>
+        <v>107844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135175716</v>
       </c>
       <c r="B6" t="n">
-        <v>107789</v>
+        <v>107844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97571090</v>
+        <v>135630886</v>
       </c>
       <c r="B7" t="n">
-        <v>58238</v>
+        <v>107844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,42 +1303,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Klintaberget/Skybygget, Ög</t>
+          <t>Kalkdoserarvägen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558471</v>
+        <v>558456</v>
       </c>
       <c r="R7" t="n">
-        <v>6510056</v>
+        <v>6510079</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,12 +1369,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,72 +1383,82 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Patricia Karlsteen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Patricia Karlsteen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97571090</t>
+          <t>https://artportalen.se/Sighting/135630886</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109553273</v>
+        <v>97571090</v>
       </c>
       <c r="B8" t="n">
-        <v>58602</v>
+        <v>58238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getnäs, Ög</t>
+          <t>Klintaberget/Skybygget, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558205</v>
+        <v>558471</v>
       </c>
       <c r="R8" t="n">
-        <v>6509459</v>
+        <v>6510056</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,22 +1482,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,16 +1502,129 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Karlsson</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Karlsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97571090</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>109553273</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Getnäs, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>558205</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6509459</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/109553273</t>
         </is>
@@ -1519,6 +1639,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 209-2025 artfynd.xlsx
+++ b/artfynd/S 209-2025 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>134976479</v>
       </c>
       <c r="B5" t="n">
-        <v>107844</v>
+        <v>107871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135175716</v>
       </c>
       <c r="B6" t="n">
-        <v>107844</v>
+        <v>107871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135630886</v>
       </c>
       <c r="B7" t="n">
-        <v>107844</v>
+        <v>107871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 209-2025 artfynd.xlsx
+++ b/artfynd/S 209-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97571090</v>
+        <v>135175716</v>
       </c>
       <c r="B6" t="n">
-        <v>58238</v>
+        <v>107876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,39 +1179,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klintaberget/Skybygget, Ög</t>
+          <t>Kolvtorpsvägen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558471</v>
+        <v>544644</v>
       </c>
       <c r="R6" t="n">
-        <v>6510056</v>
+        <v>6517365</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,12 +1249,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,69 +1263,86 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Patricia Karlsteen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Patricia Karlsteen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97571090</t>
+          <t>https://artportalen.se/Sighting/135175716</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109553273</v>
+        <v>135630886</v>
       </c>
       <c r="B7" t="n">
-        <v>58602</v>
+        <v>107876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Getnäs, Ög</t>
+          <t>Kalkdoserarvägen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558205</v>
+        <v>558456</v>
       </c>
       <c r="R7" t="n">
-        <v>6509459</v>
+        <v>6510079</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1341,22 +1369,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,22 +1383,248 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Karlsson</t>
+          <t>Patricia Karlsteen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Karlsson</t>
+          <t>Patricia Karlsteen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630886</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97571090</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klintaberget/Skybygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>558471</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6510056</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97571090</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>109553273</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Getnäs, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>558205</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6509459</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/109553273</t>
         </is>
@@ -1394,6 +1638,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 209-2025 artfynd.xlsx
+++ b/artfynd/S 209-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>135630886</v>
       </c>
       <c r="B7" t="n">
-        <v>107876</v>
+        <v>107878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 209-2025 artfynd.xlsx
+++ b/artfynd/S 209-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>135630886</v>
       </c>
       <c r="B7" t="n">
-        <v>107878</v>
+        <v>107901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 209-2025 artfynd.xlsx
+++ b/artfynd/S 209-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>135630886</v>
       </c>
       <c r="B7" t="n">
-        <v>107901</v>
+        <v>107903</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 209-2025 artfynd.xlsx
+++ b/artfynd/S 209-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>135630886</v>
       </c>
       <c r="B7" t="n">
-        <v>107903</v>
+        <v>107904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 209-2025 artfynd.xlsx
+++ b/artfynd/S 209-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>135630886</v>
       </c>
       <c r="B7" t="n">
-        <v>107904</v>
+        <v>107905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 209-2025 artfynd.xlsx
+++ b/artfynd/S 209-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>135630886</v>
       </c>
       <c r="B7" t="n">
-        <v>107905</v>
+        <v>107911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
